--- a/data/trans_orig/IP33-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP33-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>521</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2948</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>652</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>709</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6481</t>
+          <t>6388</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5927</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9148</t>
+          <t>8958</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9086</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20627</t>
+          <t>20484</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>13148</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25651</t>
+          <t>26403</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24539</t>
+          <t>24132</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42149</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80644</t>
+          <t>81515</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93607</t>
+          <t>93219</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>89780</t>
+          <t>89176</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>103741</t>
+          <t>103562</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,47 +1235,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>85,83%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>185133</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>176577</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>195020</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>81,62%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>77,85%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>85,98%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>185133</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>175125</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>193916</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>81,62%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>77,21%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>85,49%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10332</t>
+          <t>10877</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>7266</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15507</t>
+          <t>15029</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7985</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>8728</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>5782</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16731</t>
+          <t>16341</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>12776</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11614</t>
+          <t>11531</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24558</t>
+          <t>24562</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16851</t>
+          <t>16783</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31071</t>
+          <t>31712</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16114</t>
+          <t>15703</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30944</t>
+          <t>30994</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35409</t>
+          <t>36383</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56444</t>
+          <t>57722</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>203652</t>
+          <t>203336</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>221911</t>
+          <t>222531</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>206712</t>
+          <t>206977</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>224090</t>
+          <t>225176</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>416872</t>
+          <t>415970</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>443053</t>
+          <t>441877</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,26%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2821</t>
+          <t>2799</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10804</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14246</t>
+          <t>13848</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>6976</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9734</t>
+          <t>10255</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>11930</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13427</t>
+          <t>14283</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>9756</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>21457</t>
+          <t>22441</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>12311</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2428</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>6903</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18189</t>
+          <t>17899</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>96773</t>
+          <t>95936</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>110529</t>
+          <t>110740</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>117346</t>
+          <t>117747</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>130109</t>
+          <t>130273</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>218292</t>
+          <t>218975</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>238278</t>
+          <t>237740</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,36%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12075</t>
+          <t>10956</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15209</t>
+          <t>15680</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11918</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5366</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>15536</t>
+          <t>15323</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10147</t>
+          <t>9896</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>4466</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14538</t>
+          <t>14087</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>8369</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21403</t>
+          <t>20689</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2370</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11245</t>
+          <t>11722</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4848</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14766</t>
+          <t>15979</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>168266</t>
+          <t>167383</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>181404</t>
+          <t>181275</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>174753</t>
+          <t>175153</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>189629</t>
+          <t>189805</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>347740</t>
+          <t>347451</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>367088</t>
+          <t>368230</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>92,02%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10241</t>
+          <t>10624</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23781</t>
+          <t>23246</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,82 +3476,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>12985</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>8049</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>19522</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>29010</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>21137</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>37957</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>1,51%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>12985</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>8438</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>20176</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>29010</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>21119</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>38971</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18465</t>
+          <t>17968</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14547</t>
+          <t>15014</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14050</t>
+          <t>13880</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>28382</t>
+          <t>28952</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17333</t>
+          <t>17670</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33642</t>
+          <t>33322</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18513</t>
+          <t>19017</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>34807</t>
+          <t>34667</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>39977</t>
+          <t>39912</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>62140</t>
+          <t>62719</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>37361</t>
+          <t>36793</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>58204</t>
+          <t>59733</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>40936</t>
+          <t>42069</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>65081</t>
+          <t>64579</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>85091</t>
+          <t>85955</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>116114</t>
+          <t>119022</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>566588</t>
+          <t>564877</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>596165</t>
+          <t>594431</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>606269</t>
+          <t>604551</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>635390</t>
+          <t>635215</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1183118</t>
+          <t>1175933</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1224746</t>
+          <t>1220337</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,02%</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>4575</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -4488,62 +4488,62 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5275</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4247</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>852</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>4269</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>667</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>4222</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>617</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5809</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22249</t>
+          <t>22011</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37554</t>
+          <t>37971</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25077</t>
+          <t>25521</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41268</t>
+          <t>41716</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50445</t>
+          <t>50122</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72914</t>
+          <t>73911</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,3%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>104839</t>
+          <t>103004</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>120516</t>
+          <t>120636</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>102570</t>
+          <t>102423</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>119238</t>
+          <t>118362</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>212627</t>
+          <t>212577</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>235200</t>
+          <t>236351</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,89%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>440</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>4462</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14960</t>
+          <t>15674</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>5891</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16068</t>
+          <t>16462</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12400</t>
+          <t>11652</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27894</t>
+          <t>26089</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17017</t>
+          <t>17080</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13368</t>
+          <t>12332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25202</t>
+          <t>25326</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22519</t>
+          <t>22524</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39993</t>
+          <t>39940</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18084</t>
+          <t>18503</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34182</t>
+          <t>35146</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45563</t>
+          <t>44885</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68834</t>
+          <t>66649</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>174531</t>
+          <t>174534</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>196029</t>
+          <t>195874</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>215044</t>
+          <t>214993</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>235409</t>
+          <t>234660</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>395241</t>
+          <t>398364</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>424462</t>
+          <t>425406</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,2%</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9452</t>
+          <t>9124</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10423</t>
+          <t>11104</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12297</t>
+          <t>13093</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12307</t>
+          <t>12722</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9788</t>
+          <t>9594</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22798</t>
+          <t>21987</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>7182</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3344</t>
+          <t>3766</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12264</t>
+          <t>12789</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>7754</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19972</t>
+          <t>18961</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11957</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13640</t>
+          <t>12871</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27822</t>
+          <t>26893</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>123370</t>
+          <t>122811</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>138289</t>
+          <t>137981</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>128300</t>
+          <t>128138</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>142798</t>
+          <t>142937</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>256932</t>
+          <t>257148</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>278204</t>
+          <t>277590</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,14%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11158</t>
+          <t>11065</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16602</t>
+          <t>17067</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2420</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10680</t>
+          <t>10343</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>6649</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17083</t>
+          <t>17289</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>11243</t>
+          <t>10290</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>24302</t>
+          <t>24502</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13646</t>
+          <t>13428</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16178</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12440</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>26700</t>
+          <t>26913</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14185</t>
+          <t>14370</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9486</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7618</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19188</t>
+          <t>19630</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>136367</t>
+          <t>135551</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>151578</t>
+          <t>151599</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>138356</t>
+          <t>138475</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>154201</t>
+          <t>154718</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>279012</t>
+          <t>279227</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>301426</t>
+          <t>303199</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,63%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3761</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11987</t>
+          <t>12392</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>7016</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17910</t>
+          <t>18292</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>12995</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>26651</t>
+          <t>27293</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16404</t>
+          <t>16528</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31331</t>
+          <t>32495</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>21590</t>
+          <t>21080</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>38557</t>
+          <t>39027</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>41786</t>
+          <t>42429</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>65497</t>
+          <t>65070</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16425</t>
+          <t>17162</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>32763</t>
+          <t>32781</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14446</t>
+          <t>14392</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>28988</t>
+          <t>29327</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>34972</t>
+          <t>34903</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>57645</t>
+          <t>56919</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>67442</t>
+          <t>67080</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>95705</t>
+          <t>94861</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>58339</t>
+          <t>56958</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>85476</t>
+          <t>83477</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>132542</t>
+          <t>132476</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>168441</t>
+          <t>172726</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>556665</t>
+          <t>558042</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>591460</t>
+          <t>591356</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>601566</t>
+          <t>603011</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>636165</t>
+          <t>637232</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1170805</t>
+          <t>1170122</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1220342</t>
+          <t>1219588</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,4%</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6629</t>
+          <t>6398</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>699</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6703</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8856</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31293</t>
+          <t>32135</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47920</t>
+          <t>47917</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30622</t>
+          <t>31445</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47944</t>
+          <t>49003</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68196</t>
+          <t>67005</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91673</t>
+          <t>92328</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80123</t>
+          <t>80921</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>97752</t>
+          <t>97314</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73074</t>
+          <t>72536</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89949</t>
+          <t>89638</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>157162</t>
+          <t>157561</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>182401</t>
+          <t>182981</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,71%</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3463</t>
+          <t>3584</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11736</t>
+          <t>11954</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9694</t>
+          <t>9448</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,47 +8862,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>3,67%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>11770</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>7247</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>17619</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>3,77%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>11770</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>7253</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>18621</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10829</t>
+          <t>10056</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7263</t>
+          <t>7618</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18741</t>
+          <t>19438</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12709</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27314</t>
+          <t>26150</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30033</t>
+          <t>30372</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48517</t>
+          <t>48241</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38931</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58755</t>
+          <t>59298</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73225</t>
+          <t>73658</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100578</t>
+          <t>101049</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>146850</t>
+          <t>146975</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>167057</t>
+          <t>167214</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>179721</t>
+          <t>179586</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>202523</t>
+          <t>202699</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>333968</t>
+          <t>332966</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>364200</t>
+          <t>363408</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,77%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8242</t>
+          <t>7756</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>3790</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13306</t>
+          <t>13263</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18056</t>
+          <t>17797</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21715</t>
+          <t>21935</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5856</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15813</t>
+          <t>16227</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18002</t>
+          <t>17311</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33777</t>
+          <t>33686</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5860</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16677</t>
+          <t>16596</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14544</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13020</t>
+          <t>13098</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27043</t>
+          <t>27256</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18178</t>
+          <t>18316</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34540</t>
+          <t>34485</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>13273</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27039</t>
+          <t>26795</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34934</t>
+          <t>35443</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56251</t>
+          <t>56161</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>124059</t>
+          <t>123773</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>144600</t>
+          <t>144849</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>132645</t>
+          <t>131992</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>151651</t>
+          <t>151949</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>261944</t>
+          <t>261634</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>290080</t>
+          <t>291047</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,1%</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12335</t>
+          <t>12701</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13995</t>
+          <t>14534</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11066</t>
+          <t>11554</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25746</t>
+          <t>26168</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16398</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19984</t>
+          <t>20729</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>37120</t>
+          <t>37454</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8833</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12419</t>
+          <t>12921</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>18451</t>
+          <t>18487</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10170</t>
+          <t>10051</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23365</t>
+          <t>21882</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8660</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>21072</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20990</t>
+          <t>21041</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38959</t>
+          <t>38265</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>125211</t>
+          <t>124813</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>143044</t>
+          <t>143711</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>127255</t>
+          <t>127711</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>145466</t>
+          <t>145780</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>256691</t>
+          <t>258052</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>283912</t>
+          <t>284364</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,87%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>10715</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9597</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23143</t>
+          <t>22788</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14388</t>
+          <t>14308</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>29795</t>
+          <t>29363</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29245</t>
+          <t>29673</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49530</t>
+          <t>51774</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18826</t>
+          <t>18785</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34571</t>
+          <t>35969</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10913,7 +10913,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>53143</t>
+          <t>51692</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>79115</t>
+          <t>78815</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16215</t>
+          <t>16257</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>31789</t>
+          <t>31139</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>22210</t>
+          <t>22856</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>40093</t>
+          <t>41008</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>42080</t>
+          <t>41820</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>66969</t>
+          <t>65921</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>105056</t>
+          <t>102944</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>136283</t>
+          <t>137340</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>104703</t>
+          <t>103168</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>137988</t>
+          <t>137808</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>217216</t>
+          <t>217136</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>264103</t>
+          <t>263803</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>495563</t>
+          <t>495523</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>533920</t>
+          <t>534862</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>532673</t>
+          <t>533092</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>570164</t>
+          <t>572240</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1040893</t>
+          <t>1040888</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1096709</t>
+          <t>1095270</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,68%</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>393</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>776</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>5553</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -11777,7 +11777,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3287</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>493</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5516</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>951</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>377</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>440</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9484</t>
+          <t>9576</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18757</t>
+          <t>18925</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10963</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20871</t>
+          <t>20981</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22728</t>
+          <t>23255</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37601</t>
+          <t>37929</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,89%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35950</t>
+          <t>35535</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45808</t>
+          <t>45303</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36121</t>
+          <t>36226</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47003</t>
+          <t>47300</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>75057</t>
+          <t>74290</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>90641</t>
+          <t>89419</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,17%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>490</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5598</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4439</t>
+          <t>4504</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14363</t>
+          <t>14577</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6043</t>
+          <t>5996</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17240</t>
+          <t>17425</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6545</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1597</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12380</t>
+          <t>12508</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2283</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9643</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11367</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6817</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18141</t>
+          <t>18278</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21915</t>
+          <t>22236</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39356</t>
+          <t>38488</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21050</t>
+          <t>21406</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37763</t>
+          <t>38483</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46121</t>
+          <t>47171</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68577</t>
+          <t>71873</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>109065</t>
+          <t>110413</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>128445</t>
+          <t>127392</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>123429</t>
+          <t>123932</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>143780</t>
+          <t>143837</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>240229</t>
+          <t>239092</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>267269</t>
+          <t>267392</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,52%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20980</t>
+          <t>18690</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12684</t>
+          <t>11915</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24075</t>
+          <t>26131</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>6426</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17446</t>
+          <t>17790</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>17531</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14447</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30853</t>
+          <t>29701</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3715</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12542</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13145</t>
+          <t>12085</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>7396</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18262</t>
+          <t>19576</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12520</t>
+          <t>12265</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26537</t>
+          <t>26677</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21010</t>
+          <t>20295</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40239</t>
+          <t>40276</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37272</t>
+          <t>36794</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>60310</t>
+          <t>60714</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>119084</t>
+          <t>119946</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>140370</t>
+          <t>140452</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>148785</t>
+          <t>148220</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>173213</t>
+          <t>171720</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>275552</t>
+          <t>276343</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>307151</t>
+          <t>309634</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>80,31%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13314</t>
+          <t>11549</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8019</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15089</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12587</t>
+          <t>13613</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30164</t>
+          <t>31345</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17414</t>
+          <t>16816</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>52427</t>
+          <t>47855</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>36032</t>
+          <t>35318</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>73782</t>
+          <t>72347</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14508</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8647</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25462</t>
+          <t>24598</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15750</t>
+          <t>15090</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>36058</t>
+          <t>34222</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18482</t>
+          <t>19082</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37805</t>
+          <t>37886</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30804</t>
+          <t>29742</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>73553</t>
+          <t>82673</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>54939</t>
+          <t>55159</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>104693</t>
+          <t>105129</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>196830</t>
+          <t>197217</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>229329</t>
+          <t>231130</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>188762</t>
+          <t>185638</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>232574</t>
+          <t>233004</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>394006</t>
+          <t>392486</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>454013</t>
+          <t>455191</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,63%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25017</t>
+          <t>25746</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12573</t>
+          <t>12771</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27902</t>
+          <t>29718</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>21780</t>
+          <t>21368</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>46252</t>
+          <t>44705</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>27029</t>
+          <t>26834</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>47490</t>
+          <t>47442</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,7 +14515,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>32342</t>
+          <t>31431</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>68954</t>
+          <t>67480</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>62669</t>
+          <t>65665</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>104192</t>
+          <t>106116</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15446</t>
+          <t>15533</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>29858</t>
+          <t>30452</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18063</t>
+          <t>17664</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>38736</t>
+          <t>37978</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>36832</t>
+          <t>37225</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>61083</t>
+          <t>62214</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>74030</t>
+          <t>72798</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>107396</t>
+          <t>105621</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>98369</t>
+          <t>98971</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>150824</t>
+          <t>155185</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>179924</t>
+          <t>182863</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>244176</t>
+          <t>242084</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>480181</t>
+          <t>482110</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>526616</t>
+          <t>529754</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>520163</t>
+          <t>518616</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>577324</t>
+          <t>575470</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1015145</t>
+          <t>1015221</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1093698</t>
+          <t>1091761</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,67%</t>
         </is>
       </c>
     </row>
